--- a/notebooks/simulation_results/summary_results_report.xlsx
+++ b/notebooks/simulation_results/summary_results_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://computingservices-my.sharepoint.com/personal/jfj36_bath_ac_uk/Documents/00_Bath_Master/03_Dissertation/src/Goal1/setred/notebooks/simulation_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{3C5A625E-49D5-6149-B87D-B76F757DAA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C585AB-ECD3-FE4B-BAF1-C46F0AC6E169}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{3C5A625E-49D5-6149-B87D-B76F757DAA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{962404BA-438B-9144-936E-6E7EB23B62D5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -386,6 +386,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -393,9 +396,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -413,6 +413,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -700,42 +704,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M44"/>
+  <dimension ref="B1:N44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="25" t="s">
+    <row r="1" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-    </row>
-    <row r="2" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="22" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+    </row>
+    <row r="2" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="22" t="s">
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="25"/>
       <c r="M2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
@@ -754,8 +758,11 @@
       <c r="M3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
@@ -789,8 +796,11 @@
       <c r="M4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
@@ -819,7 +829,7 @@
         <v>-0.32800000000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="15" t="s">
         <v>11</v>
       </c>
@@ -848,7 +858,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
@@ -877,7 +887,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8" s="15" t="s">
         <v>13</v>
       </c>
@@ -906,7 +916,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>14</v>
       </c>
@@ -935,7 +945,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C10" s="19" t="s">
         <v>1</v>
       </c>
@@ -949,7 +959,7 @@
       <c r="I10" s="20"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
@@ -978,7 +988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1007,7 +1017,7 @@
         <v>0.58599999999999997</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1036,7 +1046,7 @@
         <v>0.79400000000000004</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
@@ -1065,7 +1075,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
@@ -1094,7 +1104,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
